--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/RiskFactor003.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/RiskFactor003.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15" conformance="strict">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr dateCompatibility="0" defaultThemeVersion="153222"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspaceGit\tams\tams\tams\tams-invest-parent\tams-invest-risk\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
@@ -10,33 +15,36 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="10" uniqueCount="10">
   <si>
     <t>风险分类</t>
   </si>
   <si>
     <t>因子分类</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>因子二级分类</t>
   </si>
   <si>
     <t>因子代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>因子名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>因子类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>变动形式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>关键点</t>
@@ -46,28 +54,23 @@
   </si>
   <si>
     <t>数据来源</t>
-  </si>
-  <si>
-    <t>因子二级分类</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -82,8 +85,8 @@
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
+      <start/>
+      <end/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -99,7 +102,75 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00E3E3E3"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -112,7 +183,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -122,39 +193,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -189,7 +260,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -231,173 +302,149 @@
         </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+            <a:gs pos="0%">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110%"/>
+                <a:satMod val="105%"/>
+                <a:tint val="67%"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50%">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105%"/>
+                <a:satMod val="103%"/>
+                <a:tint val="73%"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100%">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105%"/>
+                <a:satMod val="109%"/>
+                <a:tint val="81%"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+            <a:gs pos="0%">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103%"/>
+                <a:lumMod val="102%"/>
+                <a:tint val="94%"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50%">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110%"/>
+                <a:lumMod val="100%"/>
+                <a:shade val="100%"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100%">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99%"/>
+                <a:satMod val="120%"/>
+                <a:shade val="78%"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800%"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800%"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800%"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63%"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95%"/>
+            <a:satMod val="170%"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+            <a:gs pos="0%">
+              <a:schemeClr val="phClr">
+                <a:tint val="93%"/>
+                <a:satMod val="150%"/>
+                <a:shade val="98%"/>
+                <a:lumMod val="102%"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50%">
+              <a:schemeClr val="phClr">
+                <a:tint val="98%"/>
+                <a:satMod val="130%"/>
+                <a:shade val="90%"/>
+                <a:lumMod val="103%"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100%">
+              <a:schemeClr val="phClr">
+                <a:shade val="63%"/>
+                <a:satMod val="120%"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -422,32 +469,33 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
         <v>9</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/RiskFactor003.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/RiskFactor003.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15" conformance="strict">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr dateCompatibility="0" defaultThemeVersion="153222"/>
+  <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspaceGit\tams\tams\tams\tams-invest-parent\tams-invest-risk\src\main\resources\tpl\"/>
@@ -14,17 +14,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
-      <x14:workbookPr/>
-    </ext>
-  </extLst>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>风险分类</t>
   </si>
@@ -54,12 +49,16 @@
   </si>
   <si>
     <t>数据来源</t>
+  </si>
+  <si>
+    <t>日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -72,7 +71,6 @@
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -85,8 +83,8 @@
   </fills>
   <borders count="1">
     <border>
-      <start/>
-      <end/>
+      <left/>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -183,7 +181,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -302,25 +300,25 @@
         </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0%">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110%"/>
-                <a:satMod val="105%"/>
-                <a:tint val="67%"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50%">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105%"/>
-                <a:satMod val="103%"/>
-                <a:tint val="73%"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100%">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105%"/>
-                <a:satMod val="109%"/>
-                <a:tint val="81%"/>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -328,25 +326,25 @@
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0%">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103%"/>
-                <a:lumMod val="102%"/>
-                <a:tint val="94%"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50%">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110%"/>
-                <a:lumMod val="100%"/>
-                <a:shade val="100%"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100%">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99%"/>
-                <a:satMod val="120%"/>
-                <a:shade val="78%"/>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -359,21 +357,21 @@
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800%"/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800%"/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800%"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -387,7 +385,7 @@
           <a:effectLst>
             <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63%"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -399,32 +397,32 @@
         </a:solidFill>
         <a:solidFill>
           <a:schemeClr val="phClr">
-            <a:tint val="95%"/>
-            <a:satMod val="170%"/>
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0%">
-              <a:schemeClr val="phClr">
-                <a:tint val="93%"/>
-                <a:satMod val="150%"/>
-                <a:shade val="98%"/>
-                <a:lumMod val="102%"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50%">
-              <a:schemeClr val="phClr">
-                <a:tint val="98%"/>
-                <a:satMod val="130%"/>
-                <a:shade val="90%"/>
-                <a:lumMod val="103%"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100%">
-              <a:schemeClr val="phClr">
-                <a:shade val="63%"/>
-                <a:satMod val="120%"/>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -444,24 +442,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.625" customWidth="1"/>
     <col min="2" max="3" width="13.75" customWidth="1"/>
     <col min="4" max="4" width="19.75" customWidth="1"/>
     <col min="5" max="5" width="26.125" customWidth="1"/>
-    <col min="6" max="7" width="12.125" customWidth="1"/>
-    <col min="8" max="8" width="20.875" customWidth="1"/>
-    <col min="9" max="9" width="19.25" customWidth="1"/>
-    <col min="10" max="10" width="17.25" customWidth="1"/>
-    <col min="11" max="11" width="19.25" customWidth="1"/>
-    <col min="12" max="12" width="18.25" customWidth="1"/>
-    <col min="13" max="13" width="15.625" customWidth="1"/>
+    <col min="6" max="8" width="12.125" customWidth="1"/>
+    <col min="9" max="9" width="20.875" customWidth="1"/>
+    <col min="10" max="10" width="19.25" customWidth="1"/>
+    <col min="11" max="11" width="17.25" customWidth="1"/>
+    <col min="12" max="12" width="19.25" customWidth="1"/>
+    <col min="13" max="13" width="18.25" customWidth="1"/>
+    <col min="14" max="14" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -484,12 +482,15 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/RiskFactor003.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/RiskFactor003.xlsx
@@ -1,57 +1,54 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspaceGit\tams\tams\tams\tams-invest-parent\tams-invest-risk\src\main\resources\tpl\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>风险分类</t>
   </si>
   <si>
     <t>因子分类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>因子代码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>因子名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>因子类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变动形式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关键点</t>
+  </si>
+  <si>
+    <t>数值</t>
+  </si>
+  <si>
+    <t>数据来源</t>
   </si>
   <si>
     <t>因子二级分类</t>
-  </si>
-  <si>
-    <t>因子代码</t>
-  </si>
-  <si>
-    <t>因子名称</t>
-  </si>
-  <si>
-    <t>因子类型</t>
-  </si>
-  <si>
-    <t>变动形式</t>
-  </si>
-  <si>
-    <t>关键点</t>
-  </si>
-  <si>
-    <t>数值</t>
-  </si>
-  <si>
-    <t>数据来源</t>
-  </si>
-  <si>
-    <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -64,13 +61,15 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -100,75 +99,7 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00E3E3E3"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -181,7 +112,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -191,39 +122,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -258,7 +189,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -302,164 +233,188 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.625" customWidth="1"/>
     <col min="2" max="3" width="13.75" customWidth="1"/>
     <col min="4" max="4" width="19.75" customWidth="1"/>
     <col min="5" max="5" width="26.125" customWidth="1"/>
-    <col min="6" max="8" width="12.125" customWidth="1"/>
-    <col min="9" max="9" width="20.875" customWidth="1"/>
-    <col min="10" max="10" width="19.25" customWidth="1"/>
-    <col min="11" max="11" width="17.25" customWidth="1"/>
-    <col min="12" max="12" width="19.25" customWidth="1"/>
-    <col min="13" max="13" width="18.25" customWidth="1"/>
-    <col min="14" max="14" width="15.625" customWidth="1"/>
+    <col min="6" max="7" width="12.125" customWidth="1"/>
+    <col min="8" max="8" width="20.875" customWidth="1"/>
+    <col min="9" max="9" width="19.25" customWidth="1"/>
+    <col min="10" max="10" width="17.25" customWidth="1"/>
+    <col min="11" max="11" width="19.25" customWidth="1"/>
+    <col min="12" max="12" width="18.25" customWidth="1"/>
+    <col min="13" max="13" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -467,36 +422,32 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>10</v>
       </c>
       <c r="I1" t="s">
         <v>7</v>
       </c>
       <c r="J1" t="s">
         <v>8</v>
-      </c>
-      <c r="K1" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>